--- a/tests/testdata/excel/フォルダ/深い/階層/の/フォルダ/テスト/深い階層.xlsx
+++ b/tests/testdata/excel/フォルダ/深い/階層/の/フォルダ/テスト/深い階層.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC53BC00-35E5-4A90-89F7-1317C8D1FECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABC2052D-B216-4D6A-9EF3-8CC6395316B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{D5A67D05-E22A-4BB7-A2A5-8751121B358B}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{52C575BA-A6CA-4E0A-B2B1-A5ED63BE2522}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB8819CF-376F-4BDD-8877-67BA7688E594}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77F47511-0C58-462F-85FE-358FCC3BB737}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/フォルダ/深い/階層/の/フォルダ/テスト/深い階層.xlsx
+++ b/tests/testdata/excel/フォルダ/深い/階層/の/フォルダ/テスト/深い階層.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABC2052D-B216-4D6A-9EF3-8CC6395316B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A02298EC-4AA1-44B2-BFA6-314C1FF3F0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{52C575BA-A6CA-4E0A-B2B1-A5ED63BE2522}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{ED27A7D4-8BDE-47D1-8410-B2ECA815CB60}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77F47511-0C58-462F-85FE-358FCC3BB737}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9969E23-D15D-4B05-BCF7-CF08E7CE436E}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
